--- a/r4-core-107-IndexPage-Update/all-profiles.xlsx
+++ b/r4-core-107-IndexPage-Update/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:32:10+00:00</t>
+    <t>2024-11-16T16:15:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
